--- a/us/processed/state_per_disease/腸チフス.xlsx
+++ b/us/processed/state_per_disease/腸チフス.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -463,6 +463,16 @@
           <t>2026-W15</t>
         </is>
       </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -488,6 +498,12 @@
       <c r="G2" t="n">
         <v>3</v>
       </c>
+      <c r="H2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -513,6 +529,12 @@
       <c r="G3" t="n">
         <v>0</v>
       </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -538,6 +560,12 @@
       <c r="G4" t="n">
         <v>0</v>
       </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -563,6 +591,12 @@
       <c r="G5" t="n">
         <v>0</v>
       </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -588,6 +622,12 @@
       <c r="G6" t="n">
         <v>0</v>
       </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -613,6 +653,12 @@
       <c r="G7" t="n">
         <v>6</v>
       </c>
+      <c r="H7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I7" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -638,6 +684,12 @@
       <c r="G8" t="n">
         <v>3</v>
       </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -663,6 +715,12 @@
       <c r="G9" t="n">
         <v>0</v>
       </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -688,6 +746,12 @@
       <c r="G10" t="n">
         <v>0</v>
       </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -713,6 +777,12 @@
       <c r="G11" t="n">
         <v>0</v>
       </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -738,6 +808,12 @@
       <c r="G12" t="n">
         <v>0</v>
       </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -763,6 +839,12 @@
       <c r="G13" t="n">
         <v>0</v>
       </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -788,6 +870,12 @@
       <c r="G14" t="n">
         <v>0</v>
       </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -813,6 +901,12 @@
       <c r="G15" t="n">
         <v>0</v>
       </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -838,6 +932,12 @@
       <c r="G16" t="n">
         <v>0</v>
       </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -863,6 +963,12 @@
       <c r="G17" t="n">
         <v>0</v>
       </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -888,6 +994,12 @@
       <c r="G18" t="n">
         <v>0</v>
       </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -913,6 +1025,12 @@
       <c r="G19" t="n">
         <v>0</v>
       </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -938,6 +1056,12 @@
       <c r="G20" t="n">
         <v>0</v>
       </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -963,6 +1087,12 @@
       <c r="G21" t="n">
         <v>0</v>
       </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -988,6 +1118,12 @@
       <c r="G22" t="n">
         <v>0</v>
       </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1013,6 +1149,12 @@
       <c r="G23" t="n">
         <v>0</v>
       </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1038,6 +1180,12 @@
       <c r="G24" t="n">
         <v>0</v>
       </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1063,6 +1211,12 @@
       <c r="G25" t="n">
         <v>3</v>
       </c>
+      <c r="H25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1088,6 +1242,12 @@
       <c r="G26" t="n">
         <v>4</v>
       </c>
+      <c r="H26" t="n">
+        <v>4</v>
+      </c>
+      <c r="I26" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1113,6 +1273,12 @@
       <c r="G27" t="n">
         <v>1</v>
       </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1138,6 +1304,12 @@
       <c r="G28" t="n">
         <v>0</v>
       </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1163,6 +1335,12 @@
       <c r="G29" t="n">
         <v>0</v>
       </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1188,6 +1366,12 @@
       <c r="G30" t="n">
         <v>0</v>
       </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1213,6 +1397,12 @@
       <c r="G31" t="n">
         <v>0</v>
       </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1238,6 +1428,12 @@
       <c r="G32" t="n">
         <v>1</v>
       </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1263,6 +1459,12 @@
       <c r="G33" t="n">
         <v>1</v>
       </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1288,6 +1490,12 @@
       <c r="G34" t="n">
         <v>1</v>
       </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1313,6 +1521,12 @@
       <c r="G35" t="n">
         <v>0</v>
       </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1338,6 +1552,12 @@
       <c r="G36" t="n">
         <v>0</v>
       </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1363,6 +1583,12 @@
       <c r="G37" t="n">
         <v>1</v>
       </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1388,6 +1614,12 @@
       <c r="G38" t="n">
         <v>1</v>
       </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1413,6 +1645,12 @@
       <c r="G39" t="n">
         <v>1</v>
       </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1438,6 +1676,12 @@
       <c r="G40" t="n">
         <v>0</v>
       </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1463,6 +1707,12 @@
       <c r="G41" t="n">
         <v>0</v>
       </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1488,6 +1738,12 @@
       <c r="G42" t="n">
         <v>0</v>
       </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1513,6 +1769,12 @@
       <c r="G43" t="n">
         <v>0</v>
       </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1538,6 +1800,12 @@
       <c r="G44" t="n">
         <v>1</v>
       </c>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1563,6 +1831,12 @@
       <c r="G45" t="n">
         <v>0</v>
       </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1588,6 +1862,12 @@
       <c r="G46" t="n">
         <v>0</v>
       </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1613,6 +1893,12 @@
       <c r="G47" t="n">
         <v>0</v>
       </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1638,6 +1924,12 @@
       <c r="G48" t="n">
         <v>0</v>
       </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1663,6 +1955,12 @@
       <c r="G49" t="n">
         <v>0</v>
       </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1688,6 +1986,12 @@
       <c r="G50" t="n">
         <v>3</v>
       </c>
+      <c r="H50" t="n">
+        <v>3</v>
+      </c>
+      <c r="I50" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1713,6 +2017,12 @@
       <c r="G51" t="n">
         <v>0</v>
       </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1738,6 +2048,12 @@
       <c r="G52" t="n">
         <v>0</v>
       </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1763,6 +2079,12 @@
       <c r="G53" t="n">
         <v>0</v>
       </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1788,6 +2110,12 @@
       <c r="G54" t="n">
         <v>0</v>
       </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1813,6 +2141,12 @@
       <c r="G55" t="n">
         <v>1</v>
       </c>
+      <c r="H55" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1838,6 +2172,12 @@
       <c r="G56" t="n">
         <v>2</v>
       </c>
+      <c r="H56" t="n">
+        <v>2</v>
+      </c>
+      <c r="I56" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1863,6 +2203,12 @@
       <c r="G57" t="n">
         <v>0</v>
       </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1888,6 +2234,12 @@
       <c r="G58" t="n">
         <v>3</v>
       </c>
+      <c r="H58" t="n">
+        <v>3</v>
+      </c>
+      <c r="I58" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1911,6 +2263,12 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2200,7 +2558,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2340,7 +2698,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
